--- a/AT/PackSizeCalc.xlsx
+++ b/AT/PackSizeCalc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wellspan-my.sharepoint.com/personal/dsmith14_wellspan_org/Documents/Documents/GitHub/dps/AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{0D167D5A-055E-4A27-9100-735B2BE6C8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AB45680-8823-49CC-8509-906BAD8F3C6A}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{0D167D5A-055E-4A27-9100-735B2BE6C8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D836300-BE76-45A4-B182-B63DB9FDCDFB}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="1470" windowWidth="27435" windowHeight="14730" xr2:uid="{7B076A87-33F9-471E-91F6-2A1AC2BC6B91}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12630" xr2:uid="{7B076A87-33F9-471E-91F6-2A1AC2BC6B91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>cubic inch</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>Make this roll top strap a Y strap for top.  2 on back and Y to 1 on the front.  2 are 1/2" webbing and one is 1" webbing.  Could use linelocs and zingit or amsteel.</t>
+  </si>
+  <si>
+    <t>Decathalon MT100 Pack</t>
+  </si>
+  <si>
+    <t>8" Drawstring top</t>
   </si>
 </sst>
 </file>
@@ -501,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78752EC1-7E1B-4166-BA47-98EEB597644C}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -765,11 +771,11 @@
         <v>8.5</v>
       </c>
       <c r="D15">
-        <f t="shared" ref="D15:D19" si="2">IF(ISBLANK(C15),"",A15*B15*C15)</f>
+        <f t="shared" ref="D15:D22" si="2">IF(ISBLANK(C15),"",A15*B15*C15)</f>
         <v>3867.5</v>
       </c>
       <c r="E15">
-        <f t="shared" ref="E15:E19" si="3">IF(ISBLANK(C15),"", D15*$C$1)</f>
+        <f t="shared" ref="E15:E22" si="3">IF(ISBLANK(C15),"", D15*$C$1)</f>
         <v>63.376954549999994</v>
       </c>
     </row>
@@ -792,7 +798,7 @@
         <v>67.105010699999994</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>38</v>
       </c>
@@ -811,7 +817,7 @@
         <v>72.856868759999998</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>36</v>
       </c>
@@ -830,108 +836,171 @@
         <v>65.187724679999988</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D19" t="str">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>23</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+      <c r="D19">
+        <f>IF(ISBLANK(C19),"",A19*B19*C19)</f>
+        <v>2300</v>
+      </c>
+      <c r="E19">
+        <f>IF(ISBLANK(C19),"", D19*$C$1)</f>
+        <v>37.690237999999994</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>10</v>
+      </c>
+      <c r="D20">
+        <f>IF(ISBLANK(C20),"",A20*B20*C20)</f>
+        <v>3000</v>
+      </c>
+      <c r="E20">
+        <f>IF(ISBLANK(C20),"", D20*$C$1)</f>
+        <v>49.161179999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>33</v>
+      </c>
+      <c r="B21">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <f>IF(ISBLANK(C21),"",A21*B21*C21)</f>
+        <v>3960</v>
+      </c>
+      <c r="E21">
+        <f>IF(ISBLANK(C21),"", D21*$C$1)</f>
+        <v>64.892757599999996</v>
+      </c>
+      <c r="F21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="E19" t="str">
+      <c r="E22" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>23</v>
       </c>
     </row>
